--- a/data/000550_江铃汽车_财务数据.xlsx
+++ b/data/000550_江铃汽车_财务数据.xlsx
@@ -10853,7 +10853,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -17540,8 +17540,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17588,22 +17586,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -17613,75 +17611,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -17715,58 +17703,52 @@
         <v>9.243242680618483</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.7318803392097158</v>
+      <c r="J2" s="3" t="n">
+        <v>49.33861353800931</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>49.33861353800931</v>
+        <v>1.375379170879676</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.375379170879676</v>
+        <v>1.21241995281429</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.21241995281429</v>
+        <v>97.38899186074623</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>15.93892791801317</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>22.58621168574022</v>
+        <v>13.29064245087901</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>13.29064245087901</v>
+        <v>1.087366234628889</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>27.08672671998565</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.087366234628889</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.631682200024505</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="3" t="n">
+        <v>3.48478285878331</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>3449000000</v>
+      </c>
       <c r="X2" s="3" t="n">
-        <v>3.48478285878331</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>3449000000</v>
+        <v>1.169822789900605</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>1.169822789900605</v>
+        <v>2.759846331379071</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.759846331379071</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17802,64 +17784,58 @@
       <c r="I3" s="3" t="n">
         <v>6.370018370149685</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>-0.7772788278101128</v>
+      <c r="J3" s="3" t="n">
+        <v>52.34611885991512</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>52.34611885991512</v>
+        <v>1.338601284986338</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.338601284986338</v>
+        <v>1.165866627280112</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.165866627280112</v>
+        <v>109.8552338530067</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>13.53443297150259</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>26.59882395945198</v>
+        <v>14.61253760308916</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>14.61253760308916</v>
+        <v>1.232192568968906</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>24.63637800486441</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1.232192568968906</v>
-      </c>
+        <v>1.819834930593051</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.819834930593051</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>17.69094883538435</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-47.5774054737001</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>17.69094883538435</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-47.5774054737001</v>
+        <v>7.716175389891386</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0.976932455218585</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>7.716175389891386</v>
-      </c>
-      <c r="X3" s="6" t="n">
-        <v>0.976932455218585</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-344999999.9999999</v>
       </c>
+      <c r="X3" s="3" t="n">
+        <v>1.113356790156538</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="n">
-        <v>1.113356790156538</v>
+        <v>2.61524183746843</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.61524183746843</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17895,64 +17871,58 @@
       <c r="I4" s="3" t="n">
         <v>5.88882573297411</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>-0.5793641193044309</v>
+      <c r="J4" s="3" t="n">
+        <v>55.6139676026841</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>55.6139676026841</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>1.170179177519931</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.9711105848922567</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>125.3081664098613</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>9.022465561162567</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>39.9004016761925</v>
+        <v>11.7653380975108</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>11.7653380975108</v>
+        <v>1.134944644422571</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.59835569673645</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>1.134944644422571</v>
-      </c>
+        <v>1.714627153773785</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.714627153773785</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>-9.878236794006549</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-86.70889241796773</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-9.878236794006549</v>
+        <v>-11.3212553062462</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-86.70889241796773</v>
+        <v>-1.110707650791685</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-11.3212553062462</v>
+        <v>-1487000000</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-1.110707650791685</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>-1487000000</v>
+        <v>1.11475172041678</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.11475172041678</v>
+        <v>2.32251181757665</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.32251181757665</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17988,64 +17958,58 @@
       <c r="I5" s="3" t="n">
         <v>6.088787253146565</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>-0.6495829361074249</v>
+      <c r="J5" s="3" t="n">
+        <v>56.80069138647682</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>56.80069138647682</v>
-      </c>
-      <c r="L5" s="3" t="n">
         <v>1.122914183551847</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>0.9778754469606674</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>131.4851862436887</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>10.42846693905273</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>34.52089382878177</v>
+        <v>13.13216198836429</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>13.13216198836429</v>
+        <v>1.223315844599128</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>27.41361249723975</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>1.223315844599128</v>
-      </c>
+        <v>1.951479063647614</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.951479063647614</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>3.271922815654833</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>60.95686854315425</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>3.271922815654833</v>
+        <v>3.85519511048425</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.95686854315425</v>
+        <v>18.51675476749606</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>3.85519511048425</v>
+        <v>1120000000</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.51675476749606</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>1120000000</v>
+        <v>1.103050703415944</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1.103050703415944</v>
+        <v>2.260435266260899</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.260435266260899</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18081,64 +18045,58 @@
       <c r="I6" s="3" t="n">
         <v>4.060378614362408</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>-0.5969576471692941</v>
+      <c r="J6" s="3" t="n">
+        <v>61.02182011708355</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>61.02182011708355</v>
+        <v>1.150522773705084</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.150522773705084</v>
+        <v>1.025117173416657</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.025117173416657</v>
+        <v>156.5537957400328</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>12.50311056479033</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>28.79283504168844</v>
+        <v>15.8947524546356</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>15.8947524546356</v>
+        <v>1.261174211759774</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>22.64898437565842</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>1.261174211759774</v>
-      </c>
+        <v>1.934235332982671</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.934235332982671</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>13.44397855576444</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>272.5669549141986</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>13.44397855576444</v>
+        <v>15.99242767192067</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>272.5669549141986</v>
+        <v>6.715102591496096</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>15.99242767192067</v>
+        <v>2287000000</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.715102591496096</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>2287000000</v>
+        <v>1.061315043066896</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.061315043066896</v>
+        <v>2.181028138385989</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2.181028138385989</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18174,64 +18132,58 @@
       <c r="I7" s="3" t="n">
         <v>4.852216860151456</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>-0.8397063783966043</v>
-      </c>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>67.54429227208924</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>0.9861338637959282</v>
+      </c>
       <c r="L7" s="6" t="n">
-        <v>0.9861338637959282</v>
-      </c>
-      <c r="M7" s="6" t="n">
         <v>0.8705827287619942</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>208.1122150789012</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>11.51964234570728</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>31.25097022948388</v>
+        <v>17.32293875283112</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>17.32293875283112</v>
+        <v>1.291482343502493</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>20.78169328752978</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>1.291482343502493</v>
-      </c>
+        <v>1.956630546747403</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.956630546747403</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>6.422497922286202</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>4.261309315933008</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>6.422497922286202</v>
+        <v>-6.478623381231177</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>4.261309315933008</v>
+        <v>3.065315904560164</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-6.478623381231177</v>
+        <v>591000000.0000002</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>3.065315904560164</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>591000000.0000002</v>
+        <v>1.107397876651939</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>1.107397876651939</v>
+        <v>2.05124370554527</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2.05124370554527</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18267,64 +18219,58 @@
       <c r="I8" s="3" t="n">
         <v>4.927958944793262</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.5445375427699264</v>
+      <c r="J8" s="3" t="n">
+        <v>66.36085626911316</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>66.36085626911316</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>1.020446627448741</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>0.8988520189616769</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>197.2513797208094</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>7.429417213871406</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>48.45602146664302</v>
+        <v>14.86002062524367</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>14.86002062524367</v>
+        <v>1.118408376539655</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>24.22607673830849</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>1.118408376539655</v>
-      </c>
+        <v>1.733787445538852</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.733787445538852</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>-14.53955898561309</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>50.28383832531872</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-14.53955898561309</v>
+        <v>4.207291627148238</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>50.28383832531872</v>
+        <v>-1.760386648310265</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>4.207291627148238</v>
+        <v>-2900000000</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-1.760386648310265</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-2900000000</v>
+        <v>1.009292807983747</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1.009292807983747</v>
+        <v>1.914714806404201</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.914714806404201</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18360,64 +18306,58 @@
       <c r="I9" s="3" t="n">
         <v>3.877917826833748</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.6178030742593185</v>
+      <c r="J9" s="3" t="n">
+        <v>65.73556157990458</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>65.73556157990458</v>
-      </c>
-      <c r="L9" s="3" t="n">
         <v>1.050810693563256</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.9662165826148257</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>191.8477716574862</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>7.053876027435134</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>51.03577077337719</v>
+        <v>17.65852148929249</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>17.65852148929249</v>
+        <v>1.171803956296702</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>20.38675775988898</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>1.171803956296702</v>
-      </c>
+        <v>1.781035042609746</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.781035042609746</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>10.18940969161376</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>23.36552019722718</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>10.18940969161376</v>
+        <v>6.090723751274224</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>23.36552019722718</v>
+        <v>4.29123791116453</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>6.090723751274224</v>
+        <v>3271000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>4.29123791116453</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>3271000000</v>
+        <v>1.120108417223011</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.120108417223011</v>
+        <v>2.000908353470448</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>2.000908353470448</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18453,64 +18393,58 @@
       <c r="I10" s="3" t="n">
         <v>3.425689050589892</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.3969080600881627</v>
+      <c r="J10" s="3" t="n">
+        <v>65.64526588845656</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>65.64526588845656</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1.065173327789616</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.9583701470817525</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>191.0806984426616</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>8.927337617308364</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>40.32557246429555</v>
+        <v>20.79337796957123</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>20.79337796957123</v>
+        <v>1.27954388049549</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>17.31320425795268</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>1.27954388049549</v>
-      </c>
+        <v>1.924819338800692</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.924819338800692</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>15.69869036554519</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>13.21585841587335</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>15.69869036554519</v>
+        <v>5.830273497820913</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>13.21585841587335</v>
+        <v>2.184741674696463</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>5.830273497820913</v>
+        <v>822000000</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.184741674696463</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>822000000</v>
+        <v>1.077600114086018</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.077600114086018</v>
+        <v>2.180187694650996</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>2.180187694650996</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18546,64 +18480,58 @@
       <c r="I11" s="3" t="n">
         <v>3.104432818978005</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.3372395092034678</v>
+      <c r="J11" s="3" t="n">
+        <v>66.22090437361008</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>66.22090437361008</v>
+        <v>1.131693401300098</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.131693401300098</v>
+        <v>1.037599962587102</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.037599962587102</v>
+        <v>196.0410814606741</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>7.589596963572951</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>47.4333487967618</v>
+        <v>18.7140995923285</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>18.7140995923285</v>
+        <v>1.213348096615813</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.2368325402936</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>1.213348096615813</v>
-      </c>
+        <v>1.752803952611089</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.752803952611089</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>2.073658851396439</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-32.01223987375947</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>2.073658851396439</v>
+        <v>9.354734111543465</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-32.01223987375947</v>
+        <v>2.94371529221455</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>9.354734111543465</v>
+        <v>1324000000</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>2.94371529221455</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>1324000000</v>
+        <v>1.034416471047382</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.034416471047382</v>
+        <v>2.128770769147803</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>2.128770769147803</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
